--- a/public/namuna/atoyo-mahsulotlar.xlsx
+++ b/public/namuna/atoyo-mahsulotlar.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,16 +439,17 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,55 +480,60 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>manufacturerCountry</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>supplier</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>discountPrice</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>diameterMm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>lengthMm</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>weightKg</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>isActive</t>
         </is>
@@ -557,37 +563,42 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>metr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Tebo</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Turkiya</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Akmal aka</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>45000</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
         <v>120</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>25</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>4000</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1.2</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -615,41 +626,46 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Valtec</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Italiya</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Bek ota</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>89000</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>79000</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>40</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>15</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>0.35</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://example.com/kran-1.jpg | https://example.com/kran-2.jpg</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -664,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -727,7 +743,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MAJBURIY. Faqat shu qiymatlardan biri: pipes, fittings, faucets, shower-systems, boilers, radiators, pumps, sanitary-ware</t>
+          <t>MAJBURIY. Standart: pipes, fittings, faucets, shower-systems, boilers, radiators, pumps, sanitary-ware. Admin panelda qo'shilgan yangi kategoriyaning slugi ham bo'ladi (Katalog &gt; Turlar).</t>
         </is>
       </c>
     </row>
@@ -739,137 +755,149 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MAJBURIY. Faqat: polypropylene, metal-plastic, steel, copper, brass, cast-iron, pvc</t>
+          <t>MAJBURIY. Standart: polypropylene, metal-plastic, steel, copper, brass, cast-iron, pvc (+ o'zingiz qo'shganlari).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Brend (ixtiyoriy).</t>
+          <t>Sotish turi: dona, metr, kg, litr, m2, quti, rulon, komplekt (+ o'zingiz qo'shganlari). Bo'sh qoldirilsa - dona.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>manufacturerCountry</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Ishlab chiqarilgan davlat (ixtiyoriy).</t>
+          <t>Brend (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>manufacturerCountry</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Mahsulot kimdan kelgani - bulk narx yangilashda ishlatiladi (ixtiyoriy).</t>
+          <t>Ishlab chiqarilgan davlat (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>MAJBURIY. Sotuv narxi, faqat son (45000).</t>
+          <t>Mahsulot kimdan kelgani - bulk narx yangilashda ishlatiladi (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>discountPrice</t>
+          <t>price</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Chegirma narxi (ixtiyoriy). Bo'sh - chegirma yo'q.</t>
+          <t>MAJBURIY. Sotuv narxi (sotish turiga nisbatan), faqat son: 45000.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>discountPrice</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Zaxira soni, son. Bo'sh - 0.</t>
+          <t>Chegirma narxi (ixtiyoriy). Bo'sh - chegirma yo'q.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>diameterMm</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Diametr, mm (ixtiyoriy).</t>
+          <t>Zaxira miqdori (sotish turida). Bo'sh - 0.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lengthMm</t>
+          <t>diameterMm</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Uzunlik, mm (ixtiyoriy).</t>
+          <t>Diametr, mm (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>weightKg</t>
+          <t>lengthMm</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Og'irlik, kg (ixtiyoriy).</t>
+          <t>Uzunlik, mm (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>weightKg</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Rasm HAVOLALARI (http bilan boshlanadi), bir nechtasi ' | ' bilan ajratiladi. Excel faylning o'ziga qo'yilgan rasm o'qilmaydi!</t>
+          <t>Og'irlik, kg (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>images</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Rasm HAVOLALARI (http bilan boshlanadi), bir nechtasi ' | ' bilan ajratiladi. Excel faylning o'ziga qo'yilgan rasm o'qilmaydi!</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>isActive</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>1 - saytda ko'rinadi, 0 - yashirin. Bo'sh - 1.</t>
         </is>

--- a/public/namuna/atoyo-mahsulotlar.xlsx
+++ b/public/namuna/atoyo-mahsulotlar.xlsx
@@ -430,26 +430,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,80 +461,85 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>material</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>manufacturerCountry</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>supplier</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>discountPrice</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>diameterMm</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>lengthMm</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>weightKg</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>isActive</t>
         </is>
@@ -543,62 +549,67 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
+          <t>PPR-25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>PPR quvur 25mm</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Issiq va sovuq suv uchun polipropilen quvur</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>pipes</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>polypropylene</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>metr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Tebo</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Turkiya</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Akmal aka</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>45000</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>120</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>25</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>4000</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.2</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -606,66 +617,71 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
+          <t>KR-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Latun kran 1/2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Yarim dyuymli to'p kran</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>faucets</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>brass</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>dona</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Valtec</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Italiya</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Bek ota</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>89000</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>79000</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>40</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>0.35</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>https://example.com/kran-1.jpg | https://example.com/kran-2.jpg</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -680,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -714,190 +730,202 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>sku</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>MAJBURIY. Mahsulot nomi.</t>
+          <t>Do'kon kodi / artikul (masalan HS897). Ixtiyoriy, lekin kod bo'yicha qidirish uchun qulay.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Tavsif (ixtiyoriy).</t>
+          <t>MAJBURIY. Mahsulot nomi.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MAJBURIY. Standart: pipes, fittings, faucets, shower-systems, boilers, radiators, pumps, sanitary-ware. Admin panelda qo'shilgan yangi kategoriyaning slugi ham bo'ladi (Katalog &gt; Turlar).</t>
+          <t>Tavsif (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>category</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MAJBURIY. Standart: polypropylene, metal-plastic, steel, copper, brass, cast-iron, pvc (+ o'zingiz qo'shganlari).</t>
+          <t>MAJBURIY. Standart: pipes, fittings, faucets, shower-systems, boilers, radiators, pumps, sanitary-ware (+ Katalog &gt; Turlar da qo'shganlaringiz).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>material</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sotish turi: dona, metr, kg, litr, m2, quti, rulon, komplekt (+ o'zingiz qo'shganlari). Bo'sh qoldirilsa - dona.</t>
+          <t>MAJBURIY. Standart: polypropylene, metal-plastic, steel, copper, brass, cast-iron, pvc (+ o'zingiz qo'shganlari).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Brend (ixtiyoriy).</t>
+          <t>Sotish turi: dona, metr, kg, litr, m2, quti, rulon, komplekt (+ o'zingiz qo'shganlari). Bo'sh - dona.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>manufacturerCountry</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Ishlab chiqarilgan davlat (ixtiyoriy).</t>
+          <t>Brend (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>supplier</t>
+          <t>manufacturerCountry</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Mahsulot kimdan kelgani - bulk narx yangilashda ishlatiladi (ixtiyoriy).</t>
+          <t>Ishlab chiqarilgan davlat (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>MAJBURIY. Sotuv narxi (sotish turiga nisbatan), faqat son: 45000.</t>
+          <t>Mahsulot kimdan kelgani - bulk narx yangilashda ishlatiladi (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>discountPrice</t>
+          <t>price</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Chegirma narxi (ixtiyoriy). Bo'sh - chegirma yo'q.</t>
+          <t>MAJBURIY. Sotuv narxi (sotish turiga nisbatan), faqat son: 45000.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>discountPrice</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Zaxira miqdori (sotish turida). Bo'sh - 0.</t>
+          <t>Chegirma narxi (ixtiyoriy). Bo'sh - chegirma yo'q.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>diameterMm</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Diametr, mm (ixtiyoriy).</t>
+          <t>Zaxira miqdori (sotish turida). Bo'sh - 0.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lengthMm</t>
+          <t>diameterMm</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Uzunlik, mm (ixtiyoriy).</t>
+          <t>Diametr, mm (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>weightKg</t>
+          <t>lengthMm</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Og'irlik, kg (ixtiyoriy).</t>
+          <t>Uzunlik, mm (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>weightKg</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Rasm HAVOLALARI (http bilan boshlanadi), bir nechtasi ' | ' bilan ajratiladi. Excel faylning o'ziga qo'yilgan rasm o'qilmaydi!</t>
+          <t>Og'irlik, kg (ixtiyoriy).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>images</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Rasm HAVOLALARI (http bilan boshlanadi), bir nechtasi ' | ' bilan ajratiladi. Excel faylning o'ziga qo'yilgan rasm o'qilmaydi!</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>isActive</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>1 - saytda ko'rinadi, 0 - yashirin. Bo'sh - 1.</t>
         </is>

--- a/public/namuna/atoyo-mahsulotlar.xlsx
+++ b/public/namuna/atoyo-mahsulotlar.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -47,6 +47,9 @@
     <t xml:space="preserve">discountPrice</t>
   </si>
   <si>
+    <t xml:space="preserve">retailMarkupPercent</t>
+  </si>
+  <si>
     <t xml:space="preserve">stock</t>
   </si>
   <si>
@@ -285,6 +288,12 @@
   </si>
   <si>
     <t xml:space="preserve">79000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shu mahsulotning dona ustamasi, foizda. Bo'sh bo'lsa umumiy sozlamadagi foiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
   </si>
   <si>
     <t xml:space="preserve">Zaxira (dona/metr...)</t>
@@ -428,81 +437,84 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2">
         <v>45000</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>120</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>25</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>4000</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>1.2</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3">
         <v>89000</v>
@@ -510,58 +522,55 @@
       <c r="L3">
         <v>79000</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>40</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>15</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>0.35</v>
       </c>
-      <c r="T3" t="s">
-        <v>40</v>
-      </c>
-      <c r="V3">
+      <c r="U3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4">
         <v>850000</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>4</v>
-      </c>
-      <c r="N4" t="s">
-        <v>48</v>
       </c>
       <c r="O4" t="s">
         <v>49</v>
@@ -569,89 +578,89 @@
       <c r="P4" t="s">
         <v>50</v>
       </c>
-      <c r="T4" t="s">
+      <c r="Q4" t="s">
         <v>51</v>
       </c>
-      <c r="V4">
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+      <c r="W4">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5">
         <v>990000</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>2</v>
       </c>
-      <c r="N5" t="s">
-        <v>48</v>
-      </c>
       <c r="O5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P5" t="s">
         <v>53</v>
       </c>
+      <c r="Q5" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6">
         <v>1150000</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>48</v>
-      </c>
       <c r="O6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="P6" t="s">
         <v>55</v>
       </c>
+      <c r="Q6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7">
         <v>320000</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>15</v>
-      </c>
-      <c r="N7" t="s">
-        <v>62</v>
       </c>
       <c r="O7" t="s">
         <v>63</v>
@@ -659,55 +668,58 @@
       <c r="P7" t="s">
         <v>64</v>
       </c>
-      <c r="V7">
+      <c r="Q7" t="s">
+        <v>65</v>
+      </c>
+      <c r="W7">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8">
         <v>360000</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>8</v>
       </c>
-      <c r="N8" t="s">
-        <v>62</v>
-      </c>
       <c r="O8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P8" t="s">
         <v>66</v>
       </c>
+      <c r="Q8" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="9">
       <c r="C9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9">
         <v>410000</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>6</v>
       </c>
-      <c r="N9" t="s">
-        <v>62</v>
-      </c>
       <c r="O9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P9" t="s">
         <v>68</v>
       </c>
+      <c r="Q9" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="10">
       <c r="C10" t="s">
-        <v>69</v>
-      </c>
-      <c r="U10">
+        <v>70</v>
+      </c>
+      <c r="V10">
         <v>1</v>
       </c>
     </row>
@@ -720,16 +732,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
@@ -737,13 +749,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -751,13 +763,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -765,13 +777,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -779,13 +791,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -793,13 +805,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -807,13 +819,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -821,13 +833,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -835,13 +847,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -849,13 +861,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -863,13 +875,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -877,13 +889,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -891,13 +903,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -905,36 +917,36 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="s">
         <v>94</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
         <v>95</v>
       </c>
-    </row>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
@@ -942,10 +954,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>49</v>
@@ -956,52 +968,52 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>102</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" t="s">
         <v>103</v>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="s">
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
@@ -1009,13 +1021,13 @@
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
@@ -1023,13 +1035,13 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27">
@@ -1037,13 +1049,13 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28">
@@ -1051,22 +1063,36 @@
         <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
